--- a/Teklemariam_Ex3A_tables.xlsx
+++ b/Teklemariam_Ex3A_tables.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\betty\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7803A5B-7C9D-43F1-8DB2-6C15AA6B5215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4CBC50-3B79-4890-B657-2FBAAEA87A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="216" yWindow="504" windowWidth="11016" windowHeight="11664" xr2:uid="{40770089-5A5B-4FC7-8EBC-77DEC300F2E3}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{40770089-5A5B-4FC7-8EBC-77DEC300F2E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Teklemariam_Ex3A_tables " sheetId="1" r:id="rId1"/>
+    <sheet name="Customer" sheetId="1" r:id="rId1"/>
+    <sheet name="dog info" sheetId="2" r:id="rId2"/>
+    <sheet name="walk detail" sheetId="3" r:id="rId3"/>
+    <sheet name="payment" sheetId="4" r:id="rId4"/>
+    <sheet name="Employee" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t xml:space="preserve">customer id </t>
   </si>
@@ -57,6 +61,66 @@
   </si>
   <si>
     <t>Emergency contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dog ID </t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t>Breed</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Medical notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk ID </t>
+  </si>
+  <si>
+    <t>Dog ID</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Payment ID</t>
+  </si>
+  <si>
+    <t>Walk ID</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>HireDate</t>
   </si>
 </sst>
 </file>
@@ -72,12 +136,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -92,8 +168,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +514,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -453,6 +531,146 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F081A54E-FD85-4E56-AE4B-E89EFA9A7FD0}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D22052-4582-4783-BD6A-F7A364B6DA26}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DD737A-4473-4D98-925F-98210702C5A4}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C98EBC-F02B-4253-8363-4C946CF697DA}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Teklemariam_Ex3A_tables.xlsx
+++ b/Teklemariam_Ex3A_tables.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\betty\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4CBC50-3B79-4890-B657-2FBAAEA87A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EA4E21-E1AF-424E-B832-B6A5BC14F1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{40770089-5A5B-4FC7-8EBC-77DEC300F2E3}"/>
+    <workbookView xWindow="9864" yWindow="420" windowWidth="11016" windowHeight="11664" activeTab="4" xr2:uid="{40770089-5A5B-4FC7-8EBC-77DEC300F2E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
     <sheet name="dog info" sheetId="2" r:id="rId2"/>
-    <sheet name="walk detail" sheetId="3" r:id="rId3"/>
-    <sheet name="payment" sheetId="4" r:id="rId4"/>
+    <sheet name="payment" sheetId="4" r:id="rId3"/>
+    <sheet name="walk detail" sheetId="3" r:id="rId4"/>
     <sheet name="Employee" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t xml:space="preserve">customer id </t>
   </si>
@@ -121,16 +121,63 @@
   </si>
   <si>
     <t>HireDate</t>
+  </si>
+  <si>
+    <t>chris walter</t>
+  </si>
+  <si>
+    <t>chriswalter@gmail.com</t>
+  </si>
+  <si>
+    <t>628 georgiya ave MD 20010</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>healthy</t>
+  </si>
+  <si>
+    <t>Germen shepherd</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>45 min</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Katy</t>
+  </si>
+  <si>
+    <t>katy1@lana.org</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -165,15 +212,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -506,10 +558,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C079B30-2573-4F45-B46B-2244B235E1FD}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" customWidth="1"/>
     <col min="6" max="6" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -533,17 +589,41 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>10001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>7183672118</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>7187654565</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{6FC171D8-9FB3-4C8F-AD74-EFBA99CCAC82}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F081A54E-FD85-4E56-AE4B-E89EFA9A7FD0}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
     <col min="7" max="7" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -570,40 +650,88 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>10001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D22052-4582-4783-BD6A-F7A364B6DA26}">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DD737A-4473-4D98-925F-98210702C5A4}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10001</v>
+      </c>
+      <c r="C2">
+        <v>20001</v>
+      </c>
+      <c r="D2">
+        <v>49.99</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45905</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -612,35 +740,58 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DD737A-4473-4D98-925F-98210702C5A4}">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D22052-4582-4783-BD6A-F7A364B6DA26}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>20001</v>
+      </c>
+      <c r="B2">
+        <v>1000</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45905</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -650,10 +801,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C98EBC-F02B-4253-8363-4C946CF697DA}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -673,7 +826,27 @@
         <v>25</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>5656578978</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45357</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{1EAEAE51-5FC3-42AE-81A4-1EF5087FC544}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>